--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.4%</t>
+          <t>-499.7%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.7%</t>
+          <t>-144.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-129.9%</t>
+          <t>-130.2%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.378169943573846</v>
+        <v>-3.3815856297401</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.31504120963605</v>
+        <v>2.313674935169548</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.9408721005253343</v>
+        <v>0.93745641435908</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.231188871694537</v>
+        <v>4.229139459994784</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.8%</t>
+          <t>457.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.7%</t>
+          <t>-509.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.9%</t>
+          <t>-148.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-130.2%</t>
+          <t>-139.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-28.8%</t>
         </is>
       </c>
     </row>
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.3815856297401</v>
+        <v>-3.475717430249925</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.313674935169548</v>
+        <v>2.276022214965619</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.93745641435908</v>
+        <v>0.8433246138492563</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.229139459994784</v>
+        <v>4.17266037968889</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-87.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2026"/>
+  <dimension ref="A1:G2027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.735031168950405</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
@@ -48159,6 +48159,29 @@
       </c>
       <c r="G2026" t="n">
         <v>4.17266037968889</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="2" t="n">
+        <v>45489</v>
+      </c>
+      <c r="B2027" t="n">
+        <v>3.736611053308335</v>
+      </c>
+      <c r="C2027" t="n">
+        <v>3.58991853425664</v>
+      </c>
+      <c r="D2027" t="n">
+        <v>-3.475717430249925</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>2.276022214965619</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>0.8433246138492563</v>
+      </c>
+      <c r="G2027" t="n">
+        <v>3.582982331243008</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-68.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-509.1%</t>
+          <t>-524.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.6%</t>
+          <t>-154.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.7%</t>
+          <t>-136.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.7%</t>
+          <t>-155.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-87.7%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.940854575567723</v>
+        <v>-2.097707512379874</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.432635935574996</v>
+        <v>2.369894760850135</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.236198248854152</v>
+        <v>1.079345312042</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.951053139428323</v>
+        <v>3.856941377341033</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.939013556509472</v>
+        <v>-2.095866493321623</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.431806353408448</v>
+        <v>2.369065178683588</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.23746647552562</v>
+        <v>1.080613538713469</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.950248085641356</v>
+        <v>3.856136323554066</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-1.945922262009152</v>
+        <v>-2.102775198821304</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.442116278074495</v>
+        <v>2.379375103349634</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.23746647552562</v>
+        <v>1.080613538713469</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.963321492507276</v>
+        <v>3.869209730419985</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-1.947483904824012</v>
+        <v>-2.104336841636163</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.441491620948551</v>
+        <v>2.378750446223691</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.23746647552562</v>
+        <v>1.080613538713469</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.963321492507276</v>
+        <v>3.869209730419985</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-1.975384691933485</v>
+        <v>-2.132237628745636</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.428855347231764</v>
+        <v>2.366114172506903</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.202869551382685</v>
+        <v>1.046016614570534</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.941087379148517</v>
+        <v>3.846975617061226</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-1.978417689446159</v>
+        <v>-2.13527062625831</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.424406592203893</v>
+        <v>2.361665417479033</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.199836553870012</v>
+        <v>1.04298361705786</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.936032024618111</v>
+        <v>3.84192026253082</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-1.998479010722666</v>
+        <v>-2.155331947534817</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.483088023283794</v>
+        <v>2.420346848558934</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.179775232593504</v>
+        <v>1.022922295781353</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.99070119144271</v>
+        <v>3.896589429355419</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.25519982871749</v>
+        <v>-2.412052765529641</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.520711415087711</v>
+        <v>2.457970240362851</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.07136065844969</v>
+        <v>0.914507721637538</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.065964165958269</v>
+        <v>3.971852403870978</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.409186246493631</v>
+        <v>-2.566039183305782</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.528097117122895</v>
+        <v>2.465355942398034</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.07136065844969</v>
+        <v>0.914507721637538</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.134944435103908</v>
+        <v>4.040832673016618</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.358664342665965</v>
+        <v>-2.515517279478116</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.534357080774082</v>
+        <v>2.471615906049222</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.07136065844969</v>
+        <v>0.914507721637538</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.12099563722403</v>
+        <v>4.026883875136738</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.611139496673689</v>
+        <v>-2.767992433485841</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.445237508226406</v>
+        <v>2.382496333501546</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.07136065844969</v>
+        <v>0.914507721637538</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.132866126279444</v>
+        <v>4.038754364192152</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-2.880612298595397</v>
+        <v>-3.037465235407549</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.338658921976667</v>
+        <v>2.275917747251806</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.07136065844969</v>
+        <v>0.914507721637538</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.134076660798387</v>
+        <v>4.039964898711096</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.038156370324839</v>
+        <v>-3.19500930713699</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.279763035512212</v>
+        <v>2.217021860787351</v>
       </c>
       <c r="F2021" t="n">
-        <v>1.004458853309415</v>
+        <v>0.8476059164972636</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.098057319941544</v>
+        <v>4.003945557854252</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.167006921026885</v>
+        <v>-3.323859857839036</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.223300667967583</v>
+        <v>2.160559493242722</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.9634654444586936</v>
+        <v>0.806612507646542</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.0685391273673</v>
+        <v>3.974427365280009</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.283974613665776</v>
+        <v>-3.440827550477927</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.33871764761107</v>
+        <v>2.27597647288621</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.9634654444586936</v>
+        <v>0.806612507646542</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.230743184066345</v>
+        <v>4.136631421979054</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.36869255588673</v>
+        <v>-3.525545492698881</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.299677108686503</v>
+        <v>2.236935933961642</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.8783494155306473</v>
+        <v>0.7214964787184956</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.174520204673331</v>
+        <v>4.08040844258604</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.450627374155613</v>
+        <v>-3.607480310967765</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.27713259894744</v>
+        <v>2.21439142422258</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.8684146699435671</v>
+        <v>0.7115617331314155</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.178788774889574</v>
+        <v>4.084677012802283</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.475717430249925</v>
+        <v>-3.632570367062076</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.276022214965619</v>
+        <v>2.213281040240758</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.8433246138492563</v>
+        <v>0.6864716770371047</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.17266037968889</v>
+        <v>4.078548617601599</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.736611053308335</v>
+        <v>3.716864678902795</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.58991853425664</v>
+        <v>3.50553388884902</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.475717430249925</v>
+        <v>-3.632570367062076</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.276022214965619</v>
+        <v>2.213281040240758</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.8433246138492563</v>
+        <v>0.6864716770371047</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.582982331243008</v>
+        <v>3.498597685835388</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.1%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.5%</t>
+          <t>458.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-524.8%</t>
+          <t>-499.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-145.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.9%</t>
+          <t>-136.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.3%</t>
+          <t>-139.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-29.3%</t>
         </is>
       </c>
     </row>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.097707512379874</v>
+        <v>-2.04533964265956</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.369894760850135</v>
+        <v>2.390841908738261</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.079345312042</v>
+        <v>1.131713181762315</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.856941377341033</v>
+        <v>3.888362099173222</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.095866493321623</v>
+        <v>-2.043498623601308</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.369065178683588</v>
+        <v>2.390012326571714</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.080613538713469</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.856136323554066</v>
+        <v>3.887557045386255</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.102775198821304</v>
+        <v>-2.050407329100989</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.379375103349634</v>
+        <v>2.40032225123776</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.080613538713469</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.869209730419985</v>
+        <v>3.900630452252174</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.104336841636163</v>
+        <v>-2.051968971915849</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.378750446223691</v>
+        <v>2.399697594111816</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.080613538713469</v>
+        <v>1.132981408433784</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.869209730419985</v>
+        <v>3.900630452252174</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.132237628745636</v>
+        <v>-2.079869759025322</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.366114172506903</v>
+        <v>2.387061320395029</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.046016614570534</v>
+        <v>1.098384484290849</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.846975617061226</v>
+        <v>3.878396338893415</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.13527062625831</v>
+        <v>-2.082902756537996</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.361665417479033</v>
+        <v>2.382612565367158</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.04298361705786</v>
+        <v>1.095351486778175</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.84192026253082</v>
+        <v>3.873340984363009</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.155331947534817</v>
+        <v>-2.102964077814502</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.420346848558934</v>
+        <v>2.441293996447059</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.022922295781353</v>
+        <v>1.075290165501668</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.896589429355419</v>
+        <v>3.928010151187609</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.412052765529641</v>
+        <v>-2.359684895809326</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.457970240362851</v>
+        <v>2.478917388250977</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.914507721637538</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.971852403870978</v>
+        <v>4.003273125703167</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.566039183305782</v>
+        <v>-2.513671313585467</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.465355942398034</v>
+        <v>2.48630309028616</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.914507721637538</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.040832673016618</v>
+        <v>4.072253394848807</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.515517279478116</v>
+        <v>-2.463149409757801</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.471615906049222</v>
+        <v>2.492563053937348</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.914507721637538</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.026883875136738</v>
+        <v>4.058304596968927</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.767992433485841</v>
+        <v>-2.715624563765526</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.382496333501546</v>
+        <v>2.403443481389671</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.914507721637538</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.038754364192152</v>
+        <v>4.070175086024341</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.037465235407549</v>
+        <v>-2.985097365687234</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.275917747251806</v>
+        <v>2.296864895139932</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.914507721637538</v>
+        <v>0.9668755913578532</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.039964898711096</v>
+        <v>4.071385620543285</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.19500930713699</v>
+        <v>-3.142641437416675</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.217021860787351</v>
+        <v>2.237969008675477</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8476059164972636</v>
+        <v>0.8999737862175787</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.003945557854252</v>
+        <v>4.035366279686442</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.323859857839036</v>
+        <v>-3.271491988118722</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.160559493242722</v>
+        <v>2.181506641130848</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.806612507646542</v>
+        <v>0.8589803773668572</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.974427365280009</v>
+        <v>4.005848087112199</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.440827550477927</v>
+        <v>-3.388459680757613</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.27597647288621</v>
+        <v>2.296923620774336</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.806612507646542</v>
+        <v>0.8589803773668572</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.136631421979054</v>
+        <v>4.168052143811242</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.525545492698881</v>
+        <v>-3.473177622978566</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.236935933961642</v>
+        <v>2.257883081849768</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.7214964787184956</v>
+        <v>0.7738643484388108</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.08040844258604</v>
+        <v>4.111829164418229</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.607480310967765</v>
+        <v>-3.55511244124745</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.21439142422258</v>
+        <v>2.235338572110706</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.7115617331314155</v>
+        <v>0.7639296028517306</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.084677012802283</v>
+        <v>4.116097734634472</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.632570367062076</v>
+        <v>-3.501374267847188</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.213281040240758</v>
+        <v>2.265759479926714</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6864716770371047</v>
+        <v>0.8176677762519927</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.078548617601599</v>
+        <v>4.157266277130532</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.716864678902795</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.50553388884902</v>
+        <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.632570367062076</v>
+        <v>-3.379441368002788</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.213281040240758</v>
+        <v>2.306685527108649</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6864716770371047</v>
+        <v>0.8478416733263091</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.498597685835388</v>
+        <v>4.167523502619296</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240716.xlsx
+++ b/tame_output/ON/bt/strategyON_20240716.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.5%</t>
+          <t>-499.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.2%</t>
+          <t>-139.3%</t>
         </is>
       </c>
     </row>
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.379441368002788</v>
+        <v>-3.380511695493358</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.306685527108649</v>
+        <v>2.306257396112421</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.8478416733263091</v>
+        <v>0.8468385070411739</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.167523502619296</v>
+        <v>4.166921602848216</v>
       </c>
     </row>
   </sheetData>
